--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
     <sheet name="#EquipPurity" sheetId="8" r:id="rId8"/>
     <sheet name="#EquipGradeWeight" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
@@ -975,7 +975,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="2" activeTab="5"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="138">
   <si>
     <t>!Enum</t>
   </si>
@@ -433,6 +433,10 @@
   </si>
   <si>
     <t>상자 - 최고급 (희귀~전설)</t>
+  </si>
+  <si>
+    <t>WeaponType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -975,7 +979,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1055,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C11" s="13"/>
     </row>

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -4,438 +4,279 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
     <sheet name="#Equipment" sheetId="2" r:id="rId2"/>
     <sheet name="#EquipOption" sheetId="3" r:id="rId3"/>
-    <sheet name="#EquipEnhance" sheetId="4" r:id="rId4"/>
-    <sheet name="#EquipEnhanceTier" sheetId="5" r:id="rId5"/>
-    <sheet name="#EquipPromotion" sheetId="6" r:id="rId6"/>
-    <sheet name="#EquipQuality" sheetId="7" r:id="rId7"/>
-    <sheet name="#EquipPurity" sheetId="8" r:id="rId8"/>
-    <sheet name="#EquipGradeWeight" sheetId="9" r:id="rId9"/>
+    <sheet name="#EquipQuality" sheetId="7" r:id="rId4"/>
+    <sheet name="#EquipGradeWeight" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="86">
   <si>
     <t>!Enum</t>
   </si>
   <si>
+    <t>Weapon</t>
+  </si>
+  <si>
+    <t>Helmet</t>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>Gloves</t>
+  </si>
+  <si>
+    <t>Boots</t>
+  </si>
+  <si>
+    <t>Ring</t>
+  </si>
+  <si>
+    <t>Amulet</t>
+  </si>
+  <si>
+    <t>Relic</t>
+  </si>
+  <si>
+    <t>WeaponType</t>
+  </si>
+  <si>
+    <t>DualBlades</t>
+  </si>
+  <si>
+    <t>RuneSword</t>
+  </si>
+  <si>
+    <t>CrossBow</t>
+  </si>
+  <si>
+    <t>DualPistols</t>
+  </si>
+  <si>
+    <t>!Table</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>!ID</t>
+  </si>
+  <si>
+    <t>EquipSlotType</t>
+  </si>
+  <si>
+    <t>MaxGrade</t>
+  </si>
+  <si>
+    <t>EquipOptionGroupID</t>
+  </si>
+  <si>
+    <t>WeaponSetAddress</t>
+  </si>
+  <si>
+    <t>!int</t>
+  </si>
+  <si>
+    <t>!EquipSlotTypes</t>
+  </si>
+  <si>
+    <t>!WeaponType</t>
+  </si>
+  <si>
+    <t>!ItemGradeType</t>
+  </si>
+  <si>
+    <t>!string</t>
+  </si>
+  <si>
+    <t>Mythic</t>
+  </si>
+  <si>
+    <t>WeaponSet_DualBlades_01</t>
+  </si>
+  <si>
+    <t>WeaponSet_RuneSword_01</t>
+  </si>
+  <si>
+    <t>WeaponSet_CrossBow_01</t>
+  </si>
+  <si>
+    <t>WeaponSet_DualPistols_01</t>
+  </si>
+  <si>
+    <t>EquipOption</t>
+  </si>
+  <si>
+    <t>GroupID</t>
+  </si>
+  <si>
+    <t>ItemGrade</t>
+  </si>
+  <si>
+    <t>Opt1_ID</t>
+  </si>
+  <si>
+    <t>Opt1_Val</t>
+  </si>
+  <si>
+    <t>Opt1_Step</t>
+  </si>
+  <si>
+    <t>Opt2_ID</t>
+  </si>
+  <si>
+    <t>Opt2_Val</t>
+  </si>
+  <si>
+    <t>Opt2_Step</t>
+  </si>
+  <si>
+    <t>Opt3_ID</t>
+  </si>
+  <si>
+    <t>Opt3_Val</t>
+  </si>
+  <si>
+    <t>Opt3_Step</t>
+  </si>
+  <si>
+    <t>Opt4_ID</t>
+  </si>
+  <si>
+    <t>Opt4_Val</t>
+  </si>
+  <si>
+    <t>Opt4_Step</t>
+  </si>
+  <si>
+    <t>UnlockOpt_ID</t>
+  </si>
+  <si>
+    <t>UnlockOpt_MinVal</t>
+  </si>
+  <si>
+    <t>UnlockOpt_MaxVal</t>
+  </si>
+  <si>
+    <t>!Option</t>
+  </si>
+  <si>
+    <t>!float</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>OPT_ATK_ADD</t>
+  </si>
+  <si>
+    <t>OPT_MELEE_DAMAGE_BONUS_ADD</t>
+  </si>
+  <si>
+    <t>Magic</t>
+  </si>
+  <si>
+    <t>OPT_ATK_SPEED_ADD</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>OPT_CRIT_RATE_ADD</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>OPT_CRIT_DAMAGE_ADD</t>
+  </si>
+  <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t>OPT_DAMAGE_BONUS_ADD</t>
+  </si>
+  <si>
+    <t>OPT_FINAL_DAMAGE_AMP_ADD</t>
+  </si>
+  <si>
+    <t>OPT_RANGE_DAMAGE_BONUS_ADD</t>
+  </si>
+  <si>
+    <t>OPT_MAX_HP_ADD</t>
+  </si>
+  <si>
+    <t>OPT_DEF_ADD</t>
+  </si>
+  <si>
+    <t>OPT_MOVE_SPEED_ADD</t>
+  </si>
+  <si>
+    <t>EquipQuality</t>
+  </si>
+  <si>
+    <t>MinValue</t>
+  </si>
+  <si>
+    <t>MaxValue</t>
+  </si>
+  <si>
+    <t>AssignWeight</t>
+  </si>
+  <si>
+    <t>CalcRate</t>
+  </si>
+  <si>
+    <t>EquipGradeWeight</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>필드 - 초반</t>
+  </si>
+  <si>
+    <t>필드 - 중반</t>
+  </si>
+  <si>
+    <t>필드 - 후반</t>
+  </si>
+  <si>
+    <t>보스 - 초반</t>
+  </si>
+  <si>
+    <t>보스 - 중반</t>
+  </si>
+  <si>
+    <t>보스 - 후반</t>
+  </si>
+  <si>
+    <t>던전 - 최상위</t>
+  </si>
+  <si>
+    <t>상자 - 일반 (일반~희귀)</t>
+  </si>
+  <si>
+    <t>상자 - 고급 (고급~영웅)</t>
+  </si>
+  <si>
+    <t>상자 - 최고급 (희귀~전설)</t>
+  </si>
+  <si>
+    <t>WeaponType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>EquipSlotTypes</t>
-  </si>
-  <si>
-    <t>Weapon</t>
-  </si>
-  <si>
-    <t>Helmet</t>
-  </si>
-  <si>
-    <t>Armor</t>
-  </si>
-  <si>
-    <t>Gloves</t>
-  </si>
-  <si>
-    <t>Boots</t>
-  </si>
-  <si>
-    <t>Ring</t>
-  </si>
-  <si>
-    <t>Amulet</t>
-  </si>
-  <si>
-    <t>Relic</t>
-  </si>
-  <si>
-    <t>WeaponType</t>
-  </si>
-  <si>
-    <t>DualBlades</t>
-  </si>
-  <si>
-    <t>RuneSword</t>
-  </si>
-  <si>
-    <t>CrossBow</t>
-  </si>
-  <si>
-    <t>DualPistols</t>
-  </si>
-  <si>
-    <t>!Table</t>
-  </si>
-  <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>!ID</t>
-  </si>
-  <si>
-    <t>EquipSlotType</t>
-  </si>
-  <si>
-    <t>MaxGrade</t>
-  </si>
-  <si>
-    <t>EquipOptionGroupID</t>
-  </si>
-  <si>
-    <t>WeaponSetAddress</t>
-  </si>
-  <si>
-    <t>!int</t>
-  </si>
-  <si>
-    <t>!EquipSlotTypes</t>
-  </si>
-  <si>
-    <t>!WeaponType</t>
-  </si>
-  <si>
-    <t>!ItemGradeType</t>
-  </si>
-  <si>
-    <t>!string</t>
-  </si>
-  <si>
-    <t>Mythic</t>
-  </si>
-  <si>
-    <t>WeaponSet_DualBlades_01</t>
-  </si>
-  <si>
-    <t>WeaponSet_RuneSword_01</t>
-  </si>
-  <si>
-    <t>WeaponSet_CrossBow_01</t>
-  </si>
-  <si>
-    <t>WeaponSet_DualPistols_01</t>
-  </si>
-  <si>
-    <t>EquipOption</t>
-  </si>
-  <si>
-    <t>GroupID</t>
-  </si>
-  <si>
-    <t>ItemGrade</t>
-  </si>
-  <si>
-    <t>Opt1_ID</t>
-  </si>
-  <si>
-    <t>Opt1_Val</t>
-  </si>
-  <si>
-    <t>Opt1_Step</t>
-  </si>
-  <si>
-    <t>Opt2_ID</t>
-  </si>
-  <si>
-    <t>Opt2_Val</t>
-  </si>
-  <si>
-    <t>Opt2_Step</t>
-  </si>
-  <si>
-    <t>Opt3_ID</t>
-  </si>
-  <si>
-    <t>Opt3_Val</t>
-  </si>
-  <si>
-    <t>Opt3_Step</t>
-  </si>
-  <si>
-    <t>Opt4_ID</t>
-  </si>
-  <si>
-    <t>Opt4_Val</t>
-  </si>
-  <si>
-    <t>Opt4_Step</t>
-  </si>
-  <si>
-    <t>UnlockOpt_ID</t>
-  </si>
-  <si>
-    <t>UnlockOpt_MinVal</t>
-  </si>
-  <si>
-    <t>UnlockOpt_MaxVal</t>
-  </si>
-  <si>
-    <t>!Option</t>
-  </si>
-  <si>
-    <t>!float</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>OPT_ATK_ADD</t>
-  </si>
-  <si>
-    <t>OPT_MELEE_DAMAGE_BONUS_ADD</t>
-  </si>
-  <si>
-    <t>Magic</t>
-  </si>
-  <si>
-    <t>OPT_ATK_SPEED_ADD</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>OPT_CRIT_RATE_ADD</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>OPT_CRIT_DAMAGE_ADD</t>
-  </si>
-  <si>
-    <t>Legendary</t>
-  </si>
-  <si>
-    <t>OPT_DAMAGE_BONUS_ADD</t>
-  </si>
-  <si>
-    <t>OPT_FINAL_DAMAGE_AMP_ADD</t>
-  </si>
-  <si>
-    <t>OPT_RANGE_DAMAGE_BONUS_ADD</t>
-  </si>
-  <si>
-    <t>OPT_MAX_HP_ADD</t>
-  </si>
-  <si>
-    <t>OPT_DEF_ADD</t>
-  </si>
-  <si>
-    <t>OPT_MOVE_SPEED_ADD</t>
-  </si>
-  <si>
-    <t>EquipEnhance</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>EnhanceTier</t>
-  </si>
-  <si>
-    <t>CostItemID_1</t>
-  </si>
-  <si>
-    <t>CostItemCnt_1</t>
-  </si>
-  <si>
-    <t>CostItemMult_1</t>
-  </si>
-  <si>
-    <t>CostItemID_2</t>
-  </si>
-  <si>
-    <t>CostItemCnt_2</t>
-  </si>
-  <si>
-    <t>CostItemMult_2</t>
-  </si>
-  <si>
-    <t>CostCurrencyID</t>
-  </si>
-  <si>
-    <t>CostCurrencyValue</t>
-  </si>
-  <si>
-    <t>CostCurrencyMult</t>
-  </si>
-  <si>
-    <t>!EquipEnhanceTier</t>
-  </si>
-  <si>
-    <t>!Currency</t>
-  </si>
-  <si>
-    <t>Tier_1</t>
-  </si>
-  <si>
-    <t>Tier_2</t>
-  </si>
-  <si>
-    <t>Tier_3</t>
-  </si>
-  <si>
-    <t>Tier_4</t>
-  </si>
-  <si>
-    <t>Tier_5</t>
-  </si>
-  <si>
-    <t>Tier_6</t>
-  </si>
-  <si>
-    <t>!EnumTable</t>
-  </si>
-  <si>
-    <t>EquipEnhanceTier</t>
-  </si>
-  <si>
-    <t>Grade</t>
-  </si>
-  <si>
-    <t>MinLevel</t>
-  </si>
-  <si>
-    <t>MaxLevel</t>
-  </si>
-  <si>
-    <t>EquipPromotion</t>
-  </si>
-  <si>
-    <t>FromGrade</t>
-  </si>
-  <si>
-    <t>ToGrade</t>
-  </si>
-  <si>
-    <t>CostItemID_3</t>
-  </si>
-  <si>
-    <t>CostItemCnt_3</t>
-  </si>
-  <si>
-    <t>CostItemID_4</t>
-  </si>
-  <si>
-    <t>CostItemCnt_4</t>
-  </si>
-  <si>
-    <t>EquipQuality</t>
-  </si>
-  <si>
-    <t>MinValue</t>
-  </si>
-  <si>
-    <t>MaxValue</t>
-  </si>
-  <si>
-    <t>AssignWeight</t>
-  </si>
-  <si>
-    <t>CalcRate</t>
-  </si>
-  <si>
-    <t>EquipPurity</t>
-  </si>
-  <si>
-    <t>DisplayName</t>
-  </si>
-  <si>
-    <t>OptionMultiplier</t>
-  </si>
-  <si>
-    <t>ColorHex</t>
-  </si>
-  <si>
-    <t>!EquipPurity</t>
-  </si>
-  <si>
-    <t>Purity_1</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>#FF4D4D</t>
-  </si>
-  <si>
-    <t>Purity_2</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>#FFA500</t>
-  </si>
-  <si>
-    <t>Purity_3</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>#FFFFFF</t>
-  </si>
-  <si>
-    <t>Purity_4</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>#4D94FF</t>
-  </si>
-  <si>
-    <t>Purity_5</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>#FFD700</t>
-  </si>
-  <si>
-    <t>EquipGradeWeight</t>
-  </si>
-  <si>
-    <t>Desc</t>
-  </si>
-  <si>
-    <t>필드 - 초반</t>
-  </si>
-  <si>
-    <t>필드 - 중반</t>
-  </si>
-  <si>
-    <t>필드 - 후반</t>
-  </si>
-  <si>
-    <t>보스 - 초반</t>
-  </si>
-  <si>
-    <t>보스 - 중반</t>
-  </si>
-  <si>
-    <t>보스 - 후반</t>
-  </si>
-  <si>
-    <t>던전 - 최상위</t>
-  </si>
-  <si>
-    <t>상자 - 일반 (일반~희귀)</t>
-  </si>
-  <si>
-    <t>상자 - 고급 (고급~영웅)</t>
-  </si>
-  <si>
-    <t>상자 - 최고급 (희귀~전설)</t>
-  </si>
-  <si>
-    <t>WeaponType</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -979,7 +820,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1006,52 +847,52 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" s="10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="10"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="10"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1059,28 +900,28 @@
         <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="C11" s="13"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.3">
@@ -1121,10 +962,10 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>15</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>16</v>
       </c>
       <c r="C1" s="16"/>
       <c r="D1" s="11"/>
@@ -1143,22 +984,22 @@
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="D2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="19" t="s">
+      <c r="F2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>21</v>
       </c>
       <c r="I2" s="7"/>
       <c r="L2" s="7"/>
@@ -1168,22 +1009,22 @@
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="F3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
@@ -1198,19 +1039,19 @@
         <v>1010101001</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" s="10">
         <v>1010101001</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J4" s="7"/>
       <c r="L4" s="7"/>
@@ -1223,19 +1064,19 @@
         <v>1010101002</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" s="10">
         <v>1010101002</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J5" s="7"/>
       <c r="L5" s="7"/>
@@ -1248,19 +1089,19 @@
         <v>1010101003</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6" s="10">
         <v>1010101003</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J6" s="7"/>
       <c r="L6" s="7"/>
@@ -1273,19 +1114,19 @@
         <v>1010101004</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7" s="10">
         <v>1010101004</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J7" s="7"/>
       <c r="L7" s="7"/>
@@ -1298,10 +1139,10 @@
         <v>1010202001</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" s="10">
         <v>1010202001</v>
@@ -1318,10 +1159,10 @@
         <v>1010202002</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" s="10">
         <v>1010202002</v>
@@ -1338,10 +1179,10 @@
         <v>1010203001</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" s="10">
         <v>1010203001</v>
@@ -1358,10 +1199,10 @@
         <v>1010203002</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11" s="10">
         <v>1010203002</v>
@@ -1378,10 +1219,10 @@
         <v>1010204001</v>
       </c>
       <c r="C12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F12" s="10">
         <v>1010204001</v>
@@ -1398,10 +1239,10 @@
         <v>1010204002</v>
       </c>
       <c r="C13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" s="10">
         <v>1010204002</v>
@@ -1418,10 +1259,10 @@
         <v>1010205001</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F14" s="10">
         <v>1010205001</v>
@@ -1438,10 +1279,10 @@
         <v>1010205002</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" s="10">
         <v>1010205002</v>
@@ -1458,10 +1299,10 @@
         <v>1010306001</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F16" s="10">
         <v>1010306001</v>
@@ -1478,10 +1319,10 @@
         <v>1010306002</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F17" s="10">
         <v>1010306002</v>
@@ -1498,10 +1339,10 @@
         <v>1010307001</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F18" s="10">
         <v>1010307001</v>
@@ -1518,10 +1359,10 @@
         <v>1010307002</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" s="10">
         <v>1010307002</v>
@@ -1538,10 +1379,10 @@
         <v>1010408001</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F20" s="10">
         <v>1010408001</v>
@@ -1558,10 +1399,10 @@
         <v>1010408002</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F21" s="10">
         <v>1010408002</v>
@@ -1788,10 +1629,10 @@
   <sheetData>
     <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C1" s="11"/>
       <c r="D1" s="11"/>
@@ -1811,115 +1652,115 @@
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="J2" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="K2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="M2" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="N2" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="O2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="P2" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="Q2" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="R2" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="S2" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="S2" s="10" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="G3" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="I3" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="J3" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="L3" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="M3" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="O3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="O3" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="P3" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="R3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="R3" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="S3" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -1931,10 +1772,10 @@
         <v>1010101001</v>
       </c>
       <c r="D4" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="F4" s="10">
         <v>10</v>
@@ -1943,7 +1784,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I4" s="10">
         <v>0.1</v>
@@ -1955,7 +1796,7 @@
       <c r="N4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R4" s="10">
         <v>5</v>
@@ -1973,10 +1814,10 @@
         <v>1010101001</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F5" s="10">
         <v>30</v>
@@ -1985,7 +1826,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I5" s="10">
         <v>0.15</v>
@@ -1997,7 +1838,7 @@
       <c r="N5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R5" s="10">
         <v>0.02</v>
@@ -2015,10 +1856,10 @@
         <v>1010101001</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F6" s="10">
         <v>60</v>
@@ -2027,7 +1868,7 @@
         <v>1.2</v>
       </c>
       <c r="H6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I6" s="10">
         <v>0.2</v>
@@ -2039,7 +1880,7 @@
       <c r="N6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R6" s="10">
         <v>0.1</v>
@@ -2057,10 +1898,10 @@
         <v>1010101001</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F7" s="10">
         <v>100</v>
@@ -2069,7 +1910,7 @@
         <v>1.3</v>
       </c>
       <c r="H7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I7" s="10">
         <v>0.25</v>
@@ -2081,7 +1922,7 @@
       <c r="N7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R7" s="10">
         <v>0.5</v>
@@ -2099,10 +1940,10 @@
         <v>1010101001</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F8" s="10">
         <v>150</v>
@@ -2111,7 +1952,7 @@
         <v>1.4</v>
       </c>
       <c r="H8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I8" s="10">
         <v>0.3</v>
@@ -2123,7 +1964,7 @@
       <c r="N8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R8" s="10">
         <v>0.1</v>
@@ -2141,10 +1982,10 @@
         <v>1010101001</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F9" s="10">
         <v>220</v>
@@ -2153,7 +1994,7 @@
         <v>1.5</v>
       </c>
       <c r="H9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I9" s="10">
         <v>0.4</v>
@@ -2165,7 +2006,7 @@
       <c r="N9" s="7"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R9" s="10">
         <v>0.08</v>
@@ -2183,10 +2024,10 @@
         <v>1010101002</v>
       </c>
       <c r="D10" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="F10" s="10">
         <v>10</v>
@@ -2195,7 +2036,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I10" s="10">
         <v>0.1</v>
@@ -2208,7 +2049,7 @@
       <c r="N10" s="7"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R10" s="10">
         <v>5</v>
@@ -2226,10 +2067,10 @@
         <v>1010101002</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F11" s="10">
         <v>30</v>
@@ -2238,7 +2079,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I11" s="10">
         <v>0.15</v>
@@ -2251,7 +2092,7 @@
       <c r="N11" s="7"/>
       <c r="P11" s="7"/>
       <c r="Q11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R11" s="10">
         <v>0.02</v>
@@ -2269,10 +2110,10 @@
         <v>1010101002</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F12" s="10">
         <v>60</v>
@@ -2281,7 +2122,7 @@
         <v>1.2</v>
       </c>
       <c r="H12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I12" s="10">
         <v>0.2</v>
@@ -2294,7 +2135,7 @@
       <c r="N12" s="7"/>
       <c r="P12" s="7"/>
       <c r="Q12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R12" s="10">
         <v>0.1</v>
@@ -2312,10 +2153,10 @@
         <v>1010101002</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F13" s="10">
         <v>100</v>
@@ -2324,7 +2165,7 @@
         <v>1.3</v>
       </c>
       <c r="H13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I13" s="10">
         <v>0.25</v>
@@ -2337,7 +2178,7 @@
       <c r="N13" s="7"/>
       <c r="P13" s="7"/>
       <c r="Q13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R13" s="10">
         <v>0.5</v>
@@ -2355,10 +2196,10 @@
         <v>1010101002</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F14" s="10">
         <v>150</v>
@@ -2367,7 +2208,7 @@
         <v>1.4</v>
       </c>
       <c r="H14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I14" s="10">
         <v>0.3</v>
@@ -2380,7 +2221,7 @@
       <c r="N14" s="7"/>
       <c r="P14" s="7"/>
       <c r="Q14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R14" s="10">
         <v>0.1</v>
@@ -2398,10 +2239,10 @@
         <v>1010101002</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F15" s="10">
         <v>220</v>
@@ -2410,7 +2251,7 @@
         <v>1.5</v>
       </c>
       <c r="H15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I15" s="10">
         <v>0.4</v>
@@ -2422,7 +2263,7 @@
       <c r="N15" s="7"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R15" s="10">
         <v>0.08</v>
@@ -2440,10 +2281,10 @@
         <v>1010101003</v>
       </c>
       <c r="D16" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="F16" s="10">
         <v>10</v>
@@ -2452,7 +2293,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I16" s="10">
         <v>0.1</v>
@@ -2464,7 +2305,7 @@
       <c r="N16" s="7"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R16" s="10">
         <v>5</v>
@@ -2482,10 +2323,10 @@
         <v>1010101003</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F17" s="10">
         <v>30</v>
@@ -2494,7 +2335,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I17" s="10">
         <v>0.15</v>
@@ -2506,7 +2347,7 @@
       <c r="N17" s="7"/>
       <c r="P17" s="7"/>
       <c r="Q17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R17" s="10">
         <v>0.02</v>
@@ -2524,10 +2365,10 @@
         <v>1010101003</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F18" s="10">
         <v>60</v>
@@ -2536,7 +2377,7 @@
         <v>1.2</v>
       </c>
       <c r="H18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I18" s="10">
         <v>0.2</v>
@@ -2548,7 +2389,7 @@
       <c r="N18" s="7"/>
       <c r="P18" s="7"/>
       <c r="Q18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R18" s="10">
         <v>0.1</v>
@@ -2566,10 +2407,10 @@
         <v>1010101003</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F19" s="10">
         <v>100</v>
@@ -2578,7 +2419,7 @@
         <v>1.3</v>
       </c>
       <c r="H19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I19" s="10">
         <v>0.25</v>
@@ -2590,7 +2431,7 @@
       <c r="N19" s="7"/>
       <c r="P19" s="7"/>
       <c r="Q19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R19" s="10">
         <v>0.5</v>
@@ -2608,10 +2449,10 @@
         <v>1010101003</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F20" s="10">
         <v>150</v>
@@ -2620,7 +2461,7 @@
         <v>1.4</v>
       </c>
       <c r="H20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I20" s="10">
         <v>0.3</v>
@@ -2633,7 +2474,7 @@
       <c r="N20" s="7"/>
       <c r="P20" s="7"/>
       <c r="Q20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R20" s="10">
         <v>0.1</v>
@@ -2651,10 +2492,10 @@
         <v>1010101003</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F21" s="10">
         <v>220</v>
@@ -2663,7 +2504,7 @@
         <v>1.5</v>
       </c>
       <c r="H21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I21" s="10">
         <v>0.4</v>
@@ -2676,7 +2517,7 @@
       <c r="N21" s="7"/>
       <c r="P21" s="7"/>
       <c r="Q21" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R21" s="10">
         <v>0.08</v>
@@ -2694,10 +2535,10 @@
         <v>1010101004</v>
       </c>
       <c r="D22" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="F22" s="10">
         <v>5</v>
@@ -2706,7 +2547,7 @@
         <v>0.5</v>
       </c>
       <c r="H22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I22" s="10">
         <v>0.1</v>
@@ -2719,7 +2560,7 @@
       <c r="N22" s="7"/>
       <c r="P22" s="7"/>
       <c r="Q22" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R22" s="10">
         <v>5</v>
@@ -2737,10 +2578,10 @@
         <v>1010101004</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F23" s="10">
         <v>15</v>
@@ -2749,7 +2590,7 @@
         <v>0.5</v>
       </c>
       <c r="H23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I23" s="10">
         <v>0.15</v>
@@ -2762,7 +2603,7 @@
       <c r="N23" s="7"/>
       <c r="P23" s="7"/>
       <c r="Q23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R23" s="10">
         <v>0.02</v>
@@ -2780,10 +2621,10 @@
         <v>1010101004</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F24" s="10">
         <v>30</v>
@@ -2792,7 +2633,7 @@
         <v>0.5</v>
       </c>
       <c r="H24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I24" s="10">
         <v>0.2</v>
@@ -2805,7 +2646,7 @@
       <c r="N24" s="7"/>
       <c r="P24" s="7"/>
       <c r="Q24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R24" s="10">
         <v>0.1</v>
@@ -2823,10 +2664,10 @@
         <v>1010101004</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F25" s="10">
         <v>50</v>
@@ -2835,7 +2676,7 @@
         <v>0.5</v>
       </c>
       <c r="H25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I25" s="10">
         <v>0.25</v>
@@ -2848,7 +2689,7 @@
       <c r="N25" s="7"/>
       <c r="P25" s="7"/>
       <c r="Q25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R25" s="10">
         <v>0.5</v>
@@ -2866,10 +2707,10 @@
         <v>1010101004</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F26" s="10">
         <v>75</v>
@@ -2878,7 +2719,7 @@
         <v>0.5</v>
       </c>
       <c r="H26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I26" s="10">
         <v>0.3</v>
@@ -2891,7 +2732,7 @@
       <c r="N26" s="7"/>
       <c r="P26" s="7"/>
       <c r="Q26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R26" s="10">
         <v>0.1</v>
@@ -2909,10 +2750,10 @@
         <v>1010101004</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F27" s="10">
         <v>110</v>
@@ -2921,7 +2762,7 @@
         <v>0.5</v>
       </c>
       <c r="H27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I27" s="10">
         <v>0.4</v>
@@ -2934,7 +2775,7 @@
       <c r="N27" s="7"/>
       <c r="P27" s="7"/>
       <c r="Q27" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R27" s="10">
         <v>0.08</v>
@@ -2952,10 +2793,10 @@
         <v>1010202001</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F28" s="10">
         <v>50</v>
@@ -2968,7 +2809,7 @@
       <c r="N28" s="7"/>
       <c r="P28" s="7"/>
       <c r="Q28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R28" s="10">
         <v>50</v>
@@ -2986,10 +2827,10 @@
         <v>1010202001</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F29" s="10">
         <v>100</v>
@@ -3002,7 +2843,7 @@
       <c r="N29" s="7"/>
       <c r="P29" s="7"/>
       <c r="Q29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R29" s="10">
         <v>100</v>
@@ -3020,10 +2861,10 @@
         <v>1010202001</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F30" s="10">
         <v>150</v>
@@ -3036,7 +2877,7 @@
       <c r="N30" s="7"/>
       <c r="P30" s="7"/>
       <c r="Q30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R30" s="10">
         <v>100</v>
@@ -3054,10 +2895,10 @@
         <v>1010202001</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F31" s="10">
         <v>200</v>
@@ -3070,7 +2911,7 @@
       <c r="N31" s="7"/>
       <c r="P31" s="7"/>
       <c r="Q31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R31" s="10">
         <v>150</v>
@@ -3088,10 +2929,10 @@
         <v>1010202001</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F32" s="10">
         <v>250</v>
@@ -3104,7 +2945,7 @@
       <c r="N32" s="7"/>
       <c r="P32" s="7"/>
       <c r="Q32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R32" s="10">
         <v>150</v>
@@ -3122,10 +2963,10 @@
         <v>1010202001</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F33" s="10">
         <v>300</v>
@@ -3138,7 +2979,7 @@
       <c r="N33" s="7"/>
       <c r="P33" s="7"/>
       <c r="Q33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R33" s="10">
         <v>200</v>
@@ -3156,10 +2997,10 @@
         <v>1010202002</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F34" s="10">
         <v>50</v>
@@ -3172,7 +3013,7 @@
       <c r="N34" s="7"/>
       <c r="P34" s="7"/>
       <c r="Q34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R34" s="10">
         <v>50</v>
@@ -3190,10 +3031,10 @@
         <v>1010202002</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F35" s="10">
         <v>100</v>
@@ -3206,7 +3047,7 @@
       <c r="N35" s="7"/>
       <c r="P35" s="7"/>
       <c r="Q35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R35" s="10">
         <v>100</v>
@@ -3224,10 +3065,10 @@
         <v>1010202002</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F36" s="10">
         <v>150</v>
@@ -3240,7 +3081,7 @@
       <c r="N36" s="7"/>
       <c r="P36" s="7"/>
       <c r="Q36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R36" s="10">
         <v>100</v>
@@ -3258,10 +3099,10 @@
         <v>1010202002</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F37" s="10">
         <v>200</v>
@@ -3274,7 +3115,7 @@
       <c r="N37" s="7"/>
       <c r="P37" s="7"/>
       <c r="Q37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R37" s="10">
         <v>150</v>
@@ -3292,10 +3133,10 @@
         <v>1010202002</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F38" s="10">
         <v>250</v>
@@ -3304,7 +3145,7 @@
         <v>1</v>
       </c>
       <c r="Q38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R38" s="10">
         <v>150</v>
@@ -3322,10 +3163,10 @@
         <v>1010202002</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F39" s="10">
         <v>300</v>
@@ -3334,7 +3175,7 @@
         <v>1</v>
       </c>
       <c r="Q39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R39" s="10">
         <v>200</v>
@@ -3351,10 +3192,10 @@
         <v>1010203001</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F40" s="10">
         <v>10</v>
@@ -3363,7 +3204,7 @@
         <v>0.5</v>
       </c>
       <c r="Q40" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R40" s="10">
         <v>7</v>
@@ -3380,10 +3221,10 @@
         <v>1010203001</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F41" s="10">
         <v>15</v>
@@ -3392,7 +3233,7 @@
         <v>0.5</v>
       </c>
       <c r="Q41" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R41" s="10">
         <v>15</v>
@@ -3409,10 +3250,10 @@
         <v>1010203001</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F42" s="10">
         <v>20</v>
@@ -3421,7 +3262,7 @@
         <v>0.5</v>
       </c>
       <c r="Q42" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R42" s="10">
         <v>15</v>
@@ -3439,10 +3280,10 @@
         <v>1010203001</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F43" s="10">
         <v>25</v>
@@ -3451,7 +3292,7 @@
         <v>0.5</v>
       </c>
       <c r="Q43" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R43" s="10">
         <v>20</v>
@@ -3469,10 +3310,10 @@
         <v>1010203001</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F44" s="10">
         <v>30</v>
@@ -3481,7 +3322,7 @@
         <v>0.5</v>
       </c>
       <c r="Q44" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R44" s="10">
         <v>20</v>
@@ -3498,10 +3339,10 @@
         <v>1010203001</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F45" s="10">
         <v>35</v>
@@ -3510,7 +3351,7 @@
         <v>0.5</v>
       </c>
       <c r="Q45" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R45" s="10">
         <v>30</v>
@@ -3527,10 +3368,10 @@
         <v>1010203002</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F46" s="10">
         <v>10</v>
@@ -3539,7 +3380,7 @@
         <v>0.5</v>
       </c>
       <c r="Q46" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R46" s="10">
         <v>7</v>
@@ -3556,10 +3397,10 @@
         <v>1010203002</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F47" s="10">
         <v>15</v>
@@ -3568,7 +3409,7 @@
         <v>0.5</v>
       </c>
       <c r="Q47" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R47" s="10">
         <v>15</v>
@@ -3586,10 +3427,10 @@
         <v>1010203002</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F48" s="10">
         <v>20</v>
@@ -3598,7 +3439,7 @@
         <v>0.5</v>
       </c>
       <c r="Q48" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R48" s="10">
         <v>15</v>
@@ -3616,10 +3457,10 @@
         <v>1010203002</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F49" s="10">
         <v>25</v>
@@ -3628,7 +3469,7 @@
         <v>0.5</v>
       </c>
       <c r="Q49" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R49" s="10">
         <v>20</v>
@@ -3645,10 +3486,10 @@
         <v>1010203002</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F50" s="10">
         <v>30</v>
@@ -3657,7 +3498,7 @@
         <v>0.5</v>
       </c>
       <c r="Q50" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R50" s="10">
         <v>20</v>
@@ -3674,10 +3515,10 @@
         <v>1010203002</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F51" s="10">
         <v>35</v>
@@ -3686,7 +3527,7 @@
         <v>0.5</v>
       </c>
       <c r="Q51" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R51" s="10">
         <v>30</v>
@@ -3703,10 +3544,10 @@
         <v>1010204001</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F52" s="10">
         <v>0.1</v>
@@ -3715,7 +3556,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q52" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R52" s="10">
         <v>2.5000000000000001E-2</v>
@@ -3733,10 +3574,10 @@
         <v>1010204001</v>
       </c>
       <c r="D53" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>56</v>
       </c>
       <c r="F53" s="10">
         <v>0.15</v>
@@ -3745,7 +3586,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q53" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R53" s="10">
         <v>0.05</v>
@@ -3762,10 +3603,10 @@
         <v>1010204001</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F54" s="10">
         <v>0.2</v>
@@ -3774,7 +3615,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q54" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R54" s="10">
         <v>0.1</v>
@@ -3791,10 +3632,10 @@
         <v>1010204001</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F55" s="10">
         <v>0.25</v>
@@ -3803,7 +3644,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q55" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R55" s="10">
         <v>0.15</v>
@@ -3820,10 +3661,10 @@
         <v>1010204001</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F56" s="10">
         <v>0.3</v>
@@ -3832,7 +3673,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q56" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R56" s="10">
         <v>0.2</v>
@@ -3849,10 +3690,10 @@
         <v>1010204001</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F57" s="10">
         <v>0.35</v>
@@ -3861,7 +3702,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q57" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R57" s="10">
         <v>0.25</v>
@@ -3879,10 +3720,10 @@
         <v>1010204002</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F58" s="10">
         <v>0.1</v>
@@ -3891,7 +3732,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q58" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R58" s="10">
         <v>2.5000000000000001E-2</v>
@@ -3908,10 +3749,10 @@
         <v>1010204002</v>
       </c>
       <c r="D59" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E59" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>56</v>
       </c>
       <c r="F59" s="10">
         <v>0.15</v>
@@ -3920,7 +3761,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q59" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R59" s="10">
         <v>0.05</v>
@@ -3937,10 +3778,10 @@
         <v>1010204002</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F60" s="10">
         <v>0.2</v>
@@ -3949,7 +3790,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q60" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R60" s="10">
         <v>0.1</v>
@@ -3966,10 +3807,10 @@
         <v>1010204002</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F61" s="10">
         <v>0.25</v>
@@ -3978,7 +3819,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q61" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R61" s="10">
         <v>0.15</v>
@@ -3995,10 +3836,10 @@
         <v>1010204002</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F62" s="10">
         <v>0.3</v>
@@ -4007,7 +3848,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q62" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R62" s="10">
         <v>0.2</v>
@@ -4025,10 +3866,10 @@
         <v>1010204002</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F63" s="10">
         <v>0.35</v>
@@ -4037,7 +3878,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q63" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R63" s="10">
         <v>0.25</v>
@@ -4054,10 +3895,10 @@
         <v>1010205001</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F64" s="10">
         <v>0.1</v>
@@ -4066,7 +3907,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q64" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R64" s="10">
         <v>2.5000000000000001E-2</v>
@@ -4083,10 +3924,10 @@
         <v>1010205001</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F65" s="10">
         <v>0.125</v>
@@ -4095,7 +3936,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q65" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R65" s="10">
         <v>0.05</v>
@@ -4112,10 +3953,10 @@
         <v>1010205001</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F66" s="10">
         <v>0.15</v>
@@ -4124,7 +3965,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q66" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R66" s="10">
         <v>0.1</v>
@@ -4141,10 +3982,10 @@
         <v>1010205001</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F67" s="10">
         <v>0.17499999999999999</v>
@@ -4153,7 +3994,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q67" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R67" s="10">
         <v>0.15</v>
@@ -4171,10 +4012,10 @@
         <v>1010205001</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F68" s="10">
         <v>0.2</v>
@@ -4183,7 +4024,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q68" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R68" s="10">
         <v>0.2</v>
@@ -4200,10 +4041,10 @@
         <v>1010205001</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F69" s="10">
         <v>0.22500000000000001</v>
@@ -4212,7 +4053,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q69" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R69" s="10">
         <v>0.25</v>
@@ -4229,10 +4070,10 @@
         <v>1010205002</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F70" s="10">
         <v>0.1</v>
@@ -4241,7 +4082,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q70" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R70" s="10">
         <v>2.5000000000000001E-2</v>
@@ -4258,10 +4099,10 @@
         <v>1010205002</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F71" s="10">
         <v>0.125</v>
@@ -4270,7 +4111,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q71" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R71" s="10">
         <v>0.05</v>
@@ -4287,10 +4128,10 @@
         <v>1010205002</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F72" s="10">
         <v>0.15</v>
@@ -4299,7 +4140,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q72" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R72" s="10">
         <v>0.1</v>
@@ -4317,10 +4158,10 @@
         <v>1010205002</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F73" s="10">
         <v>0.17499999999999999</v>
@@ -4329,7 +4170,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q73" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R73" s="10">
         <v>0.15</v>
@@ -4346,10 +4187,10 @@
         <v>1010205002</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F74" s="10">
         <v>0.2</v>
@@ -4358,7 +4199,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q74" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R74" s="10">
         <v>0.2</v>
@@ -4375,10 +4216,10 @@
         <v>1010205002</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F75" s="10">
         <v>0.22500000000000001</v>
@@ -4387,7 +4228,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q75" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R75" s="10">
         <v>0.25</v>
@@ -4404,10 +4245,10 @@
         <v>1010306001</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E76" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F76" s="10">
         <v>0.1</v>
@@ -4416,7 +4257,7 @@
         <v>0.01</v>
       </c>
       <c r="Q76" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R76" s="10">
         <v>0.05</v>
@@ -4433,10 +4274,10 @@
         <v>1010306001</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E77" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F77" s="10">
         <v>0.15</v>
@@ -4445,7 +4286,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q77" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R77" s="10">
         <v>0.1</v>
@@ -4462,10 +4303,10 @@
         <v>1010306001</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E78" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F78" s="10">
         <v>0.2</v>
@@ -4474,7 +4315,7 @@
         <v>0.02</v>
       </c>
       <c r="Q78" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R78" s="10">
         <v>0.15</v>
@@ -4491,10 +4332,10 @@
         <v>1010306001</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E79" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F79" s="10">
         <v>0.25</v>
@@ -4503,7 +4344,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q79" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R79" s="10">
         <v>0.2</v>
@@ -4520,10 +4361,10 @@
         <v>1010306001</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E80" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F80" s="10">
         <v>0.3</v>
@@ -4532,7 +4373,7 @@
         <v>0.03</v>
       </c>
       <c r="Q80" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R80" s="10">
         <v>0.25</v>
@@ -4549,10 +4390,10 @@
         <v>1010306001</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E81" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F81" s="10">
         <v>0.35</v>
@@ -4561,7 +4402,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q81" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R81" s="10">
         <v>0.3</v>
@@ -4578,10 +4419,10 @@
         <v>1010306002</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E82" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F82" s="10">
         <v>0.1</v>
@@ -4590,7 +4431,7 @@
         <v>0.01</v>
       </c>
       <c r="Q82" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R82" s="10">
         <v>0.05</v>
@@ -4607,10 +4448,10 @@
         <v>1010306002</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E83" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F83" s="10">
         <v>0.15</v>
@@ -4619,7 +4460,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q83" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R83" s="10">
         <v>0.1</v>
@@ -4636,10 +4477,10 @@
         <v>1010306002</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E84" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F84" s="10">
         <v>0.2</v>
@@ -4648,7 +4489,7 @@
         <v>0.02</v>
       </c>
       <c r="Q84" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R84" s="10">
         <v>0.15</v>
@@ -4665,10 +4506,10 @@
         <v>1010306002</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E85" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F85" s="10">
         <v>0.25</v>
@@ -4677,7 +4518,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q85" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R85" s="10">
         <v>0.2</v>
@@ -4694,10 +4535,10 @@
         <v>1010306002</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E86" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F86" s="10">
         <v>0.3</v>
@@ -4706,7 +4547,7 @@
         <v>0.03</v>
       </c>
       <c r="Q86" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R86" s="10">
         <v>0.25</v>
@@ -4723,10 +4564,10 @@
         <v>1010306002</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E87" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F87" s="10">
         <v>0.35</v>
@@ -4735,7 +4576,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q87" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R87" s="10">
         <v>0.3</v>
@@ -4752,10 +4593,10 @@
         <v>1010307001</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E88" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F88" s="10">
         <v>0.1</v>
@@ -4764,7 +4605,7 @@
         <v>0.01</v>
       </c>
       <c r="Q88" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R88" s="10">
         <v>0.05</v>
@@ -4781,10 +4622,10 @@
         <v>1010307001</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E89" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F89" s="10">
         <v>0.15</v>
@@ -4793,7 +4634,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q89" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R89" s="10">
         <v>0.1</v>
@@ -4810,10 +4651,10 @@
         <v>1010307001</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E90" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F90" s="10">
         <v>0.2</v>
@@ -4822,7 +4663,7 @@
         <v>0.02</v>
       </c>
       <c r="Q90" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R90" s="10">
         <v>0.15</v>
@@ -4839,10 +4680,10 @@
         <v>1010307001</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E91" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F91" s="10">
         <v>0.25</v>
@@ -4851,7 +4692,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q91" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R91" s="10">
         <v>0.2</v>
@@ -4868,10 +4709,10 @@
         <v>1010307001</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E92" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F92" s="10">
         <v>0.3</v>
@@ -4880,7 +4721,7 @@
         <v>0.03</v>
       </c>
       <c r="Q92" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R92" s="10">
         <v>0.25</v>
@@ -4897,10 +4738,10 @@
         <v>1010307001</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E93" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F93" s="10">
         <v>0.35</v>
@@ -4909,7 +4750,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q93" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R93" s="10">
         <v>0.3</v>
@@ -4926,10 +4767,10 @@
         <v>1010307002</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E94" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F94" s="10">
         <v>0.1</v>
@@ -4938,7 +4779,7 @@
         <v>0.01</v>
       </c>
       <c r="Q94" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R94" s="10">
         <v>0.05</v>
@@ -4955,10 +4796,10 @@
         <v>1010307002</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E95" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F95" s="10">
         <v>0.15</v>
@@ -4967,7 +4808,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q95" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R95" s="10">
         <v>0.1</v>
@@ -4984,10 +4825,10 @@
         <v>1010307002</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E96" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F96" s="10">
         <v>0.2</v>
@@ -4996,7 +4837,7 @@
         <v>0.02</v>
       </c>
       <c r="Q96" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R96" s="10">
         <v>0.15</v>
@@ -5013,10 +4854,10 @@
         <v>1010307002</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E97" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F97" s="10">
         <v>0.25</v>
@@ -5025,7 +4866,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q97" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R97" s="10">
         <v>0.2</v>
@@ -5042,10 +4883,10 @@
         <v>1010307002</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E98" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F98" s="10">
         <v>0.3</v>
@@ -5054,7 +4895,7 @@
         <v>0.03</v>
       </c>
       <c r="Q98" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R98" s="10">
         <v>0.25</v>
@@ -5071,10 +4912,10 @@
         <v>1010307002</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E99" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F99" s="10">
         <v>0.35</v>
@@ -5083,7 +4924,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q99" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R99" s="10">
         <v>0.3</v>
@@ -5100,10 +4941,10 @@
         <v>1010408001</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E100" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F100" s="10">
         <v>0.1</v>
@@ -5112,7 +4953,7 @@
         <v>0.01</v>
       </c>
       <c r="Q100" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R100" s="10">
         <v>0.05</v>
@@ -5129,10 +4970,10 @@
         <v>1010408001</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E101" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F101" s="10">
         <v>0.15</v>
@@ -5141,7 +4982,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q101" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R101" s="10">
         <v>0.1</v>
@@ -5158,10 +4999,10 @@
         <v>1010408001</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E102" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F102" s="10">
         <v>0.2</v>
@@ -5170,7 +5011,7 @@
         <v>0.02</v>
       </c>
       <c r="Q102" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R102" s="10">
         <v>0.15</v>
@@ -5187,10 +5028,10 @@
         <v>1010408001</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E103" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F103" s="10">
         <v>0.25</v>
@@ -5199,7 +5040,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q103" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R103" s="10">
         <v>0.2</v>
@@ -5216,10 +5057,10 @@
         <v>1010408001</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E104" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F104" s="10">
         <v>0.3</v>
@@ -5228,7 +5069,7 @@
         <v>0.03</v>
       </c>
       <c r="Q104" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R104" s="10">
         <v>0.25</v>
@@ -5245,10 +5086,10 @@
         <v>1010408001</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E105" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F105" s="10">
         <v>0.35</v>
@@ -5257,7 +5098,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q105" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R105" s="10">
         <v>0.3</v>
@@ -5274,10 +5115,10 @@
         <v>1010408002</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E106" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F106" s="10">
         <v>0.1</v>
@@ -5286,7 +5127,7 @@
         <v>0.01</v>
       </c>
       <c r="Q106" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R106" s="10">
         <v>0.05</v>
@@ -5303,10 +5144,10 @@
         <v>1010408002</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E107" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F107" s="10">
         <v>0.15</v>
@@ -5315,7 +5156,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q107" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R107" s="10">
         <v>0.1</v>
@@ -5332,10 +5173,10 @@
         <v>1010408002</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E108" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F108" s="10">
         <v>0.2</v>
@@ -5344,7 +5185,7 @@
         <v>0.02</v>
       </c>
       <c r="Q108" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R108" s="10">
         <v>0.15</v>
@@ -5361,10 +5202,10 @@
         <v>1010408002</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E109" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F109" s="10">
         <v>0.25</v>
@@ -5373,7 +5214,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q109" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R109" s="10">
         <v>0.2</v>
@@ -5390,10 +5231,10 @@
         <v>1010408002</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E110" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F110" s="10">
         <v>0.3</v>
@@ -5402,7 +5243,7 @@
         <v>0.03</v>
       </c>
       <c r="Q110" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R110" s="10">
         <v>0.25</v>
@@ -5419,10 +5260,10 @@
         <v>1010408002</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E111" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F111" s="10">
         <v>0.35</v>
@@ -5431,7 +5272,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q111" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R111" s="10">
         <v>0.3</v>
@@ -5447,1630 +5288,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M51"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9" style="8" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.375" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.875" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9" style="10" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="10">
-        <v>1</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="10">
-        <v>2</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="10">
-        <v>3</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B7" s="10">
-        <v>4</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B8" s="10">
-        <v>5</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="10">
-        <v>6</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="10">
-        <v>7</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="10">
-        <v>8</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="10">
-        <v>9</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B13" s="10">
-        <v>10</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B14" s="10">
-        <v>11</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="10">
-        <v>12</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="10">
-        <v>13</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B17" s="10">
-        <v>14</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="10">
-        <v>15</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="10">
-        <v>16</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="10">
-        <v>17</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B21" s="10">
-        <v>18</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B22" s="10">
-        <v>19</v>
-      </c>
-      <c r="C22" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B23" s="10">
-        <v>20</v>
-      </c>
-      <c r="C23" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B24" s="10">
-        <v>21</v>
-      </c>
-      <c r="C24" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="10">
-        <v>22</v>
-      </c>
-      <c r="C25" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B26" s="10">
-        <v>23</v>
-      </c>
-      <c r="C26" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B27" s="10">
-        <v>24</v>
-      </c>
-      <c r="C27" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B28" s="10">
-        <v>25</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B29" s="10">
-        <v>26</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
-      <c r="B30" s="10">
-        <v>27</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B31" s="10">
-        <v>28</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B32" s="10">
-        <v>29</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B33" s="10">
-        <v>30</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B34" s="10">
-        <v>31</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
-      <c r="B35" s="10">
-        <v>32</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B36" s="10">
-        <v>33</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B37" s="10">
-        <v>34</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B38" s="10">
-        <v>35</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B39" s="10">
-        <v>36</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="5"/>
-      <c r="B40" s="10">
-        <v>37</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B41" s="10">
-        <v>38</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B42" s="10">
-        <v>39</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B43" s="10">
-        <v>40</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B44" s="10">
-        <v>41</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B45" s="10">
-        <v>42</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B46" s="10">
-        <v>43</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B47" s="10">
-        <v>44</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B48" s="10">
-        <v>45</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B49" s="10">
-        <v>46</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B50" s="10">
-        <v>47</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B51" s="10">
-        <v>48</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" t="s">
-        <v>87</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.25" style="10" customWidth="1"/>
-    <col min="5" max="5" width="9.375" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="10" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="10">
-        <v>1</v>
-      </c>
-      <c r="E4" s="10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="10">
-        <v>21</v>
-      </c>
-      <c r="E5" s="10">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="10">
-        <v>41</v>
-      </c>
-      <c r="E6" s="10">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="10">
-        <v>61</v>
-      </c>
-      <c r="E7" s="10">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="10">
-        <v>81</v>
-      </c>
-      <c r="E8" s="10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="10">
-        <v>101</v>
-      </c>
-      <c r="E9" s="10">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="5"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O51"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9" style="8" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.375" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.25" style="10" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.875" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9" style="10" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="10">
-        <v>1</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="10">
-        <v>2</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="10">
-        <v>3</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="10">
-        <v>4</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B8" s="10">
-        <v>5</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="10">
-        <v>6</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="10">
-        <v>7</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="10">
-        <v>8</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="10">
-        <v>9</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="10">
-        <v>10</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="10">
-        <v>11</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="10">
-        <v>12</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B16" s="10">
-        <v>13</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="10">
-        <v>14</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="10">
-        <v>15</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="10">
-        <v>16</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="10">
-        <v>17</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="10">
-        <v>18</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="10">
-        <v>19</v>
-      </c>
-      <c r="C22" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="10">
-        <v>20</v>
-      </c>
-      <c r="C23" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="10">
-        <v>21</v>
-      </c>
-      <c r="C24" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="10">
-        <v>22</v>
-      </c>
-      <c r="C25" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="10">
-        <v>23</v>
-      </c>
-      <c r="C26" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="10">
-        <v>24</v>
-      </c>
-      <c r="C27" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="10">
-        <v>25</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B29" s="10">
-        <v>26</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
-      <c r="B30" s="10">
-        <v>27</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="10">
-        <v>28</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="10">
-        <v>29</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="10">
-        <v>30</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="5"/>
-      <c r="B34" s="10">
-        <v>31</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="10">
-        <v>32</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="10">
-        <v>33</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B37" s="10">
-        <v>34</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B38" s="10">
-        <v>35</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="10">
-        <v>36</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B40" s="10">
-        <v>37</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B41" s="10">
-        <v>38</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B42" s="10">
-        <v>39</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B43" s="10">
-        <v>40</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B44" s="10">
-        <v>41</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B45" s="10">
-        <v>42</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B46" s="10">
-        <v>43</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B47" s="10">
-        <v>44</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B48" s="10">
-        <v>45</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="10">
-        <v>46</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="10">
-        <v>47</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="10">
-        <v>48</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -7087,10 +5304,10 @@
   <sheetData>
     <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="11"/>
@@ -7098,37 +5315,37 @@
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -7255,220 +5472,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.875" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.875" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.375" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="10" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="11"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D4" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="E4" s="10">
-        <v>300</v>
-      </c>
-      <c r="F4">
-        <f>E4/SUM(E4:E8)</f>
-        <v>0.3</v>
-      </c>
-      <c r="G4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="E5" s="10">
-        <v>350</v>
-      </c>
-      <c r="F5">
-        <f>E5/SUM(E4:E8)</f>
-        <v>0.35</v>
-      </c>
-      <c r="G5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D6" s="10">
-        <v>1</v>
-      </c>
-      <c r="E6" s="10">
-        <v>220</v>
-      </c>
-      <c r="F6">
-        <f>E6/SUM(E4:E8)</f>
-        <v>0.22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D7" s="10">
-        <v>1.2</v>
-      </c>
-      <c r="E7" s="10">
-        <v>100</v>
-      </c>
-      <c r="F7">
-        <f>E7/SUM(E4:E8)</f>
-        <v>0.1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" s="10">
-        <v>1.4</v>
-      </c>
-      <c r="E8" s="10">
-        <v>30</v>
-      </c>
-      <c r="F8">
-        <f>E8/SUM(E4:E8)</f>
-        <v>0.03</v>
-      </c>
-      <c r="G8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="5"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5" style="10" customWidth="1"/>
+    <col min="3" max="3" width="25.125" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.75" style="10" customWidth="1"/>
     <col min="5" max="5" width="9.875" style="10" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="10" customWidth="1"/>
@@ -7481,10 +5492,10 @@
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -7494,55 +5505,55 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -7551,7 +5562,7 @@
         <v>10001</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="D4" s="10">
         <v>800</v>
@@ -7578,7 +5589,7 @@
         <v>10002</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="D5" s="10">
         <v>400</v>
@@ -7605,7 +5616,7 @@
         <v>10003</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="D6" s="10">
         <v>100</v>
@@ -7631,7 +5642,7 @@
         <v>20001</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="D7" s="10">
         <v>400</v>
@@ -7657,7 +5668,7 @@
         <v>20002</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="D8" s="10">
         <v>100</v>
@@ -7684,7 +5695,7 @@
         <v>20003</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="D9" s="10">
         <v>0</v>
@@ -7711,7 +5722,7 @@
         <v>30001</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="D10" s="10">
         <v>0</v>
@@ -7737,7 +5748,7 @@
         <v>40001</v>
       </c>
       <c r="C11" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="D11">
         <v>700</v>
@@ -7763,7 +5774,7 @@
         <v>40002</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -7789,7 +5800,7 @@
         <v>40003</v>
       </c>
       <c r="C13" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="D13">
         <v>0</v>

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="89">
   <si>
     <t>!Enum</t>
   </si>
@@ -50,18 +50,6 @@
     <t>WeaponType</t>
   </si>
   <si>
-    <t>DualBlades</t>
-  </si>
-  <si>
-    <t>RuneSword</t>
-  </si>
-  <si>
-    <t>CrossBow</t>
-  </si>
-  <si>
-    <t>DualPistols</t>
-  </si>
-  <si>
     <t>!Table</t>
   </si>
   <si>
@@ -80,9 +68,6 @@
     <t>EquipOptionGroupID</t>
   </si>
   <si>
-    <t>WeaponSetAddress</t>
-  </si>
-  <si>
     <t>!int</t>
   </si>
   <si>
@@ -99,18 +84,6 @@
   </si>
   <si>
     <t>Mythic</t>
-  </si>
-  <si>
-    <t>WeaponSet_DualBlades_01</t>
-  </si>
-  <si>
-    <t>WeaponSet_RuneSword_01</t>
-  </si>
-  <si>
-    <t>WeaponSet_CrossBow_01</t>
-  </si>
-  <si>
-    <t>WeaponSet_DualPistols_01</t>
   </si>
   <si>
     <t>EquipOption</t>
@@ -277,6 +250,54 @@
   </si>
   <si>
     <t>EquipSlotTypes</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreatSword</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blade</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pistol</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rifle</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_GreatSword_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blade</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_Blade_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pistol</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_Pistol_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rifle</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_Rifle_01</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -847,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C1" s="13"/>
     </row>
@@ -900,28 +921,28 @@
         <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C11" s="13"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="10" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="10" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="10" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.3">
@@ -947,7 +968,7 @@
     <col min="4" max="4" width="19.75" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.25" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.625" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.25" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.75" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.125" style="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.75" style="10" bestFit="1" customWidth="1"/>
@@ -962,10 +983,10 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C1" s="16"/>
       <c r="D1" s="11"/>
@@ -984,22 +1005,22 @@
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="17" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="I2" s="7"/>
       <c r="L2" s="7"/>
@@ -1009,22 +1030,22 @@
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="15" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
@@ -1042,16 +1063,16 @@
         <v>1</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F4" s="10">
         <v>1010101001</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="J4" s="7"/>
       <c r="L4" s="7"/>
@@ -1067,16 +1088,16 @@
         <v>1</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F5" s="10">
         <v>1010101002</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="J5" s="7"/>
       <c r="L5" s="7"/>
@@ -1092,16 +1113,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F6" s="10">
         <v>1010101003</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="J6" s="7"/>
       <c r="L6" s="7"/>
@@ -1117,16 +1138,16 @@
         <v>1</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F7" s="10">
         <v>1010101004</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="J7" s="7"/>
       <c r="L7" s="7"/>
@@ -1142,7 +1163,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F8" s="10">
         <v>1010202001</v>
@@ -1162,7 +1183,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F9" s="10">
         <v>1010202002</v>
@@ -1182,7 +1203,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F10" s="10">
         <v>1010203001</v>
@@ -1202,7 +1223,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F11" s="10">
         <v>1010203002</v>
@@ -1222,7 +1243,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F12" s="10">
         <v>1010204001</v>
@@ -1242,7 +1263,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F13" s="10">
         <v>1010204002</v>
@@ -1262,7 +1283,7 @@
         <v>5</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F14" s="10">
         <v>1010205001</v>
@@ -1282,7 +1303,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F15" s="10">
         <v>1010205002</v>
@@ -1302,7 +1323,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F16" s="10">
         <v>1010306001</v>
@@ -1322,7 +1343,7 @@
         <v>6</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F17" s="10">
         <v>1010306002</v>
@@ -1342,7 +1363,7 @@
         <v>7</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F18" s="10">
         <v>1010307001</v>
@@ -1362,7 +1383,7 @@
         <v>7</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F19" s="10">
         <v>1010307002</v>
@@ -1382,7 +1403,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F20" s="10">
         <v>1010408001</v>
@@ -1402,7 +1423,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F21" s="10">
         <v>1010408002</v>
@@ -1505,7 +1526,6 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
-      <c r="G33" s="7"/>
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
       <c r="L33" s="7"/>
@@ -1514,7 +1534,6 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
-      <c r="G34" s="7"/>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
       <c r="L34" s="7"/>
@@ -1523,7 +1542,6 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
-      <c r="G35" s="7"/>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
       <c r="L35" s="7"/>
@@ -1532,7 +1550,6 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
-      <c r="G36" s="7"/>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
       <c r="L36" s="7"/>
@@ -1541,7 +1558,6 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
-      <c r="G37" s="7"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
       <c r="L37" s="7"/>
@@ -1550,7 +1566,6 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
-      <c r="G38" s="7"/>
       <c r="I38" s="7"/>
       <c r="J38" s="7"/>
       <c r="L38" s="7"/>
@@ -1559,7 +1574,6 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
-      <c r="G39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
       <c r="L39" s="7"/>
@@ -1568,7 +1582,6 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
-      <c r="G40" s="7"/>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
       <c r="L40" s="7"/>
@@ -1577,7 +1590,6 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
-      <c r="G41" s="7"/>
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
       <c r="L41" s="7"/>
@@ -1586,7 +1598,6 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
-      <c r="G42" s="7"/>
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
       <c r="L42" s="7"/>
@@ -1629,10 +1640,10 @@
   <sheetData>
     <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C1" s="11"/>
       <c r="D1" s="11"/>
@@ -1652,115 +1663,115 @@
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="17" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="M2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="N2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="O2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="P2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="Q2" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="R2" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="S2" s="10" t="s">
         <v>39</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="S2" s="10" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="15" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="R3" s="10" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="S3" s="10" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -1772,10 +1783,10 @@
         <v>1010101001</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F4" s="10">
         <v>10</v>
@@ -1784,7 +1795,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I4" s="10">
         <v>0.1</v>
@@ -1796,7 +1807,7 @@
       <c r="N4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="R4" s="10">
         <v>5</v>
@@ -1814,10 +1825,10 @@
         <v>1010101001</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F5" s="10">
         <v>30</v>
@@ -1826,7 +1837,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H5" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I5" s="10">
         <v>0.15</v>
@@ -1838,7 +1849,7 @@
       <c r="N5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R5" s="10">
         <v>0.02</v>
@@ -1856,10 +1867,10 @@
         <v>1010101001</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F6" s="10">
         <v>60</v>
@@ -1868,7 +1879,7 @@
         <v>1.2</v>
       </c>
       <c r="H6" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I6" s="10">
         <v>0.2</v>
@@ -1880,7 +1891,7 @@
       <c r="N6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="R6" s="10">
         <v>0.1</v>
@@ -1898,10 +1909,10 @@
         <v>1010101001</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F7" s="10">
         <v>100</v>
@@ -1910,7 +1921,7 @@
         <v>1.3</v>
       </c>
       <c r="H7" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I7" s="10">
         <v>0.25</v>
@@ -1922,7 +1933,7 @@
       <c r="N7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R7" s="10">
         <v>0.5</v>
@@ -1940,10 +1951,10 @@
         <v>1010101001</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F8" s="10">
         <v>150</v>
@@ -1952,7 +1963,7 @@
         <v>1.4</v>
       </c>
       <c r="H8" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I8" s="10">
         <v>0.3</v>
@@ -1964,7 +1975,7 @@
       <c r="N8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="R8" s="10">
         <v>0.1</v>
@@ -1982,10 +1993,10 @@
         <v>1010101001</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F9" s="10">
         <v>220</v>
@@ -1994,7 +2005,7 @@
         <v>1.5</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I9" s="10">
         <v>0.4</v>
@@ -2006,7 +2017,7 @@
       <c r="N9" s="7"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="12" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="R9" s="10">
         <v>0.08</v>
@@ -2024,10 +2035,10 @@
         <v>1010101002</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F10" s="10">
         <v>10</v>
@@ -2036,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I10" s="10">
         <v>0.1</v>
@@ -2049,7 +2060,7 @@
       <c r="N10" s="7"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="R10" s="10">
         <v>5</v>
@@ -2067,10 +2078,10 @@
         <v>1010101002</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F11" s="10">
         <v>30</v>
@@ -2079,7 +2090,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H11" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I11" s="10">
         <v>0.15</v>
@@ -2092,7 +2103,7 @@
       <c r="N11" s="7"/>
       <c r="P11" s="7"/>
       <c r="Q11" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R11" s="10">
         <v>0.02</v>
@@ -2110,10 +2121,10 @@
         <v>1010101002</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F12" s="10">
         <v>60</v>
@@ -2122,7 +2133,7 @@
         <v>1.2</v>
       </c>
       <c r="H12" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I12" s="10">
         <v>0.2</v>
@@ -2135,7 +2146,7 @@
       <c r="N12" s="7"/>
       <c r="P12" s="7"/>
       <c r="Q12" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="R12" s="10">
         <v>0.1</v>
@@ -2153,10 +2164,10 @@
         <v>1010101002</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F13" s="10">
         <v>100</v>
@@ -2165,7 +2176,7 @@
         <v>1.3</v>
       </c>
       <c r="H13" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I13" s="10">
         <v>0.25</v>
@@ -2178,7 +2189,7 @@
       <c r="N13" s="7"/>
       <c r="P13" s="7"/>
       <c r="Q13" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R13" s="10">
         <v>0.5</v>
@@ -2196,10 +2207,10 @@
         <v>1010101002</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F14" s="10">
         <v>150</v>
@@ -2208,7 +2219,7 @@
         <v>1.4</v>
       </c>
       <c r="H14" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I14" s="10">
         <v>0.3</v>
@@ -2221,7 +2232,7 @@
       <c r="N14" s="7"/>
       <c r="P14" s="7"/>
       <c r="Q14" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="R14" s="10">
         <v>0.1</v>
@@ -2239,10 +2250,10 @@
         <v>1010101002</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F15" s="10">
         <v>220</v>
@@ -2251,7 +2262,7 @@
         <v>1.5</v>
       </c>
       <c r="H15" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I15" s="10">
         <v>0.4</v>
@@ -2263,7 +2274,7 @@
       <c r="N15" s="7"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="12" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="R15" s="10">
         <v>0.08</v>
@@ -2281,10 +2292,10 @@
         <v>1010101003</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F16" s="10">
         <v>10</v>
@@ -2293,7 +2304,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I16" s="10">
         <v>0.1</v>
@@ -2305,7 +2316,7 @@
       <c r="N16" s="7"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="R16" s="10">
         <v>5</v>
@@ -2323,10 +2334,10 @@
         <v>1010101003</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F17" s="10">
         <v>30</v>
@@ -2335,7 +2346,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H17" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I17" s="10">
         <v>0.15</v>
@@ -2347,7 +2358,7 @@
       <c r="N17" s="7"/>
       <c r="P17" s="7"/>
       <c r="Q17" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R17" s="10">
         <v>0.02</v>
@@ -2365,10 +2376,10 @@
         <v>1010101003</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F18" s="10">
         <v>60</v>
@@ -2377,7 +2388,7 @@
         <v>1.2</v>
       </c>
       <c r="H18" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I18" s="10">
         <v>0.2</v>
@@ -2389,7 +2400,7 @@
       <c r="N18" s="7"/>
       <c r="P18" s="7"/>
       <c r="Q18" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="R18" s="10">
         <v>0.1</v>
@@ -2407,10 +2418,10 @@
         <v>1010101003</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F19" s="10">
         <v>100</v>
@@ -2419,7 +2430,7 @@
         <v>1.3</v>
       </c>
       <c r="H19" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I19" s="10">
         <v>0.25</v>
@@ -2431,7 +2442,7 @@
       <c r="N19" s="7"/>
       <c r="P19" s="7"/>
       <c r="Q19" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R19" s="10">
         <v>0.5</v>
@@ -2449,10 +2460,10 @@
         <v>1010101003</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F20" s="10">
         <v>150</v>
@@ -2461,7 +2472,7 @@
         <v>1.4</v>
       </c>
       <c r="H20" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I20" s="10">
         <v>0.3</v>
@@ -2474,7 +2485,7 @@
       <c r="N20" s="7"/>
       <c r="P20" s="7"/>
       <c r="Q20" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="R20" s="10">
         <v>0.1</v>
@@ -2492,10 +2503,10 @@
         <v>1010101003</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F21" s="10">
         <v>220</v>
@@ -2504,7 +2515,7 @@
         <v>1.5</v>
       </c>
       <c r="H21" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I21" s="10">
         <v>0.4</v>
@@ -2517,7 +2528,7 @@
       <c r="N21" s="7"/>
       <c r="P21" s="7"/>
       <c r="Q21" s="12" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="R21" s="10">
         <v>0.08</v>
@@ -2535,10 +2546,10 @@
         <v>1010101004</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F22" s="10">
         <v>5</v>
@@ -2547,7 +2558,7 @@
         <v>0.5</v>
       </c>
       <c r="H22" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="I22" s="10">
         <v>0.1</v>
@@ -2560,7 +2571,7 @@
       <c r="N22" s="7"/>
       <c r="P22" s="7"/>
       <c r="Q22" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="R22" s="10">
         <v>5</v>
@@ -2578,10 +2589,10 @@
         <v>1010101004</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F23" s="10">
         <v>15</v>
@@ -2590,7 +2601,7 @@
         <v>0.5</v>
       </c>
       <c r="H23" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="I23" s="10">
         <v>0.15</v>
@@ -2603,7 +2614,7 @@
       <c r="N23" s="7"/>
       <c r="P23" s="7"/>
       <c r="Q23" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R23" s="10">
         <v>0.02</v>
@@ -2621,10 +2632,10 @@
         <v>1010101004</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F24" s="10">
         <v>30</v>
@@ -2633,7 +2644,7 @@
         <v>0.5</v>
       </c>
       <c r="H24" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="I24" s="10">
         <v>0.2</v>
@@ -2646,7 +2657,7 @@
       <c r="N24" s="7"/>
       <c r="P24" s="7"/>
       <c r="Q24" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="R24" s="10">
         <v>0.1</v>
@@ -2664,10 +2675,10 @@
         <v>1010101004</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F25" s="10">
         <v>50</v>
@@ -2676,7 +2687,7 @@
         <v>0.5</v>
       </c>
       <c r="H25" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="I25" s="10">
         <v>0.25</v>
@@ -2689,7 +2700,7 @@
       <c r="N25" s="7"/>
       <c r="P25" s="7"/>
       <c r="Q25" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R25" s="10">
         <v>0.5</v>
@@ -2707,10 +2718,10 @@
         <v>1010101004</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F26" s="10">
         <v>75</v>
@@ -2719,7 +2730,7 @@
         <v>0.5</v>
       </c>
       <c r="H26" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="I26" s="10">
         <v>0.3</v>
@@ -2732,7 +2743,7 @@
       <c r="N26" s="7"/>
       <c r="P26" s="7"/>
       <c r="Q26" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="R26" s="10">
         <v>0.1</v>
@@ -2750,10 +2761,10 @@
         <v>1010101004</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F27" s="10">
         <v>110</v>
@@ -2762,7 +2773,7 @@
         <v>0.5</v>
       </c>
       <c r="H27" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="I27" s="10">
         <v>0.4</v>
@@ -2775,7 +2786,7 @@
       <c r="N27" s="7"/>
       <c r="P27" s="7"/>
       <c r="Q27" s="12" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="R27" s="10">
         <v>0.08</v>
@@ -2793,10 +2804,10 @@
         <v>1010202001</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F28" s="10">
         <v>50</v>
@@ -2809,7 +2820,7 @@
       <c r="N28" s="7"/>
       <c r="P28" s="7"/>
       <c r="Q28" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="R28" s="10">
         <v>50</v>
@@ -2827,10 +2838,10 @@
         <v>1010202001</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F29" s="10">
         <v>100</v>
@@ -2843,7 +2854,7 @@
       <c r="N29" s="7"/>
       <c r="P29" s="7"/>
       <c r="Q29" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="R29" s="10">
         <v>100</v>
@@ -2861,10 +2872,10 @@
         <v>1010202001</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F30" s="10">
         <v>150</v>
@@ -2877,7 +2888,7 @@
       <c r="N30" s="7"/>
       <c r="P30" s="7"/>
       <c r="Q30" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="R30" s="10">
         <v>100</v>
@@ -2895,10 +2906,10 @@
         <v>1010202001</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F31" s="10">
         <v>200</v>
@@ -2911,7 +2922,7 @@
       <c r="N31" s="7"/>
       <c r="P31" s="7"/>
       <c r="Q31" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="R31" s="10">
         <v>150</v>
@@ -2929,10 +2940,10 @@
         <v>1010202001</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F32" s="10">
         <v>250</v>
@@ -2945,7 +2956,7 @@
       <c r="N32" s="7"/>
       <c r="P32" s="7"/>
       <c r="Q32" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="R32" s="10">
         <v>150</v>
@@ -2963,10 +2974,10 @@
         <v>1010202001</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F33" s="10">
         <v>300</v>
@@ -2979,7 +2990,7 @@
       <c r="N33" s="7"/>
       <c r="P33" s="7"/>
       <c r="Q33" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="R33" s="10">
         <v>200</v>
@@ -2997,10 +3008,10 @@
         <v>1010202002</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F34" s="10">
         <v>50</v>
@@ -3013,7 +3024,7 @@
       <c r="N34" s="7"/>
       <c r="P34" s="7"/>
       <c r="Q34" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="R34" s="10">
         <v>50</v>
@@ -3031,10 +3042,10 @@
         <v>1010202002</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F35" s="10">
         <v>100</v>
@@ -3047,7 +3058,7 @@
       <c r="N35" s="7"/>
       <c r="P35" s="7"/>
       <c r="Q35" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="R35" s="10">
         <v>100</v>
@@ -3065,10 +3076,10 @@
         <v>1010202002</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F36" s="10">
         <v>150</v>
@@ -3081,7 +3092,7 @@
       <c r="N36" s="7"/>
       <c r="P36" s="7"/>
       <c r="Q36" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="R36" s="10">
         <v>100</v>
@@ -3099,10 +3110,10 @@
         <v>1010202002</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F37" s="10">
         <v>200</v>
@@ -3115,7 +3126,7 @@
       <c r="N37" s="7"/>
       <c r="P37" s="7"/>
       <c r="Q37" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="R37" s="10">
         <v>150</v>
@@ -3133,10 +3144,10 @@
         <v>1010202002</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F38" s="10">
         <v>250</v>
@@ -3145,7 +3156,7 @@
         <v>1</v>
       </c>
       <c r="Q38" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="R38" s="10">
         <v>150</v>
@@ -3163,10 +3174,10 @@
         <v>1010202002</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F39" s="10">
         <v>300</v>
@@ -3175,7 +3186,7 @@
         <v>1</v>
       </c>
       <c r="Q39" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="R39" s="10">
         <v>200</v>
@@ -3192,10 +3203,10 @@
         <v>1010203001</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F40" s="10">
         <v>10</v>
@@ -3204,7 +3215,7 @@
         <v>0.5</v>
       </c>
       <c r="Q40" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="R40" s="10">
         <v>7</v>
@@ -3221,10 +3232,10 @@
         <v>1010203001</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F41" s="10">
         <v>15</v>
@@ -3233,7 +3244,7 @@
         <v>0.5</v>
       </c>
       <c r="Q41" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="R41" s="10">
         <v>15</v>
@@ -3250,10 +3261,10 @@
         <v>1010203001</v>
       </c>
       <c r="D42" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="F42" s="10">
         <v>20</v>
@@ -3262,7 +3273,7 @@
         <v>0.5</v>
       </c>
       <c r="Q42" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="R42" s="10">
         <v>15</v>
@@ -3280,10 +3291,10 @@
         <v>1010203001</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F43" s="10">
         <v>25</v>
@@ -3292,7 +3303,7 @@
         <v>0.5</v>
       </c>
       <c r="Q43" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="R43" s="10">
         <v>20</v>
@@ -3310,10 +3321,10 @@
         <v>1010203001</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F44" s="10">
         <v>30</v>
@@ -3322,7 +3333,7 @@
         <v>0.5</v>
       </c>
       <c r="Q44" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="R44" s="10">
         <v>20</v>
@@ -3339,10 +3350,10 @@
         <v>1010203001</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F45" s="10">
         <v>35</v>
@@ -3351,7 +3362,7 @@
         <v>0.5</v>
       </c>
       <c r="Q45" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="R45" s="10">
         <v>30</v>
@@ -3368,10 +3379,10 @@
         <v>1010203002</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F46" s="10">
         <v>10</v>
@@ -3380,7 +3391,7 @@
         <v>0.5</v>
       </c>
       <c r="Q46" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="R46" s="10">
         <v>7</v>
@@ -3397,10 +3408,10 @@
         <v>1010203002</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F47" s="10">
         <v>15</v>
@@ -3409,7 +3420,7 @@
         <v>0.5</v>
       </c>
       <c r="Q47" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="R47" s="10">
         <v>15</v>
@@ -3427,10 +3438,10 @@
         <v>1010203002</v>
       </c>
       <c r="D48" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E48" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="F48" s="10">
         <v>20</v>
@@ -3439,7 +3450,7 @@
         <v>0.5</v>
       </c>
       <c r="Q48" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="R48" s="10">
         <v>15</v>
@@ -3457,10 +3468,10 @@
         <v>1010203002</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F49" s="10">
         <v>25</v>
@@ -3469,7 +3480,7 @@
         <v>0.5</v>
       </c>
       <c r="Q49" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="R49" s="10">
         <v>20</v>
@@ -3486,10 +3497,10 @@
         <v>1010203002</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F50" s="10">
         <v>30</v>
@@ -3498,7 +3509,7 @@
         <v>0.5</v>
       </c>
       <c r="Q50" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="R50" s="10">
         <v>20</v>
@@ -3515,10 +3526,10 @@
         <v>1010203002</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F51" s="10">
         <v>35</v>
@@ -3527,7 +3538,7 @@
         <v>0.5</v>
       </c>
       <c r="Q51" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="R51" s="10">
         <v>30</v>
@@ -3544,10 +3555,10 @@
         <v>1010204001</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F52" s="10">
         <v>0.1</v>
@@ -3556,7 +3567,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q52" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R52" s="10">
         <v>2.5000000000000001E-2</v>
@@ -3574,10 +3585,10 @@
         <v>1010204001</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F53" s="10">
         <v>0.15</v>
@@ -3586,7 +3597,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q53" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R53" s="10">
         <v>0.05</v>
@@ -3603,10 +3614,10 @@
         <v>1010204001</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F54" s="10">
         <v>0.2</v>
@@ -3615,7 +3626,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q54" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R54" s="10">
         <v>0.1</v>
@@ -3632,10 +3643,10 @@
         <v>1010204001</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F55" s="10">
         <v>0.25</v>
@@ -3644,7 +3655,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q55" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R55" s="10">
         <v>0.15</v>
@@ -3661,10 +3672,10 @@
         <v>1010204001</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F56" s="10">
         <v>0.3</v>
@@ -3673,7 +3684,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q56" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R56" s="10">
         <v>0.2</v>
@@ -3690,10 +3701,10 @@
         <v>1010204001</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F57" s="10">
         <v>0.35</v>
@@ -3702,7 +3713,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q57" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R57" s="10">
         <v>0.25</v>
@@ -3720,10 +3731,10 @@
         <v>1010204002</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F58" s="10">
         <v>0.1</v>
@@ -3732,7 +3743,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q58" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R58" s="10">
         <v>2.5000000000000001E-2</v>
@@ -3749,10 +3760,10 @@
         <v>1010204002</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F59" s="10">
         <v>0.15</v>
@@ -3761,7 +3772,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q59" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R59" s="10">
         <v>0.05</v>
@@ -3778,10 +3789,10 @@
         <v>1010204002</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F60" s="10">
         <v>0.2</v>
@@ -3790,7 +3801,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q60" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R60" s="10">
         <v>0.1</v>
@@ -3807,10 +3818,10 @@
         <v>1010204002</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F61" s="10">
         <v>0.25</v>
@@ -3819,7 +3830,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q61" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R61" s="10">
         <v>0.15</v>
@@ -3836,10 +3847,10 @@
         <v>1010204002</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F62" s="10">
         <v>0.3</v>
@@ -3848,7 +3859,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q62" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R62" s="10">
         <v>0.2</v>
@@ -3866,10 +3877,10 @@
         <v>1010204002</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F63" s="10">
         <v>0.35</v>
@@ -3878,7 +3889,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q63" s="10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R63" s="10">
         <v>0.25</v>
@@ -3895,10 +3906,10 @@
         <v>1010205001</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F64" s="10">
         <v>0.1</v>
@@ -3907,7 +3918,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q64" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="R64" s="10">
         <v>2.5000000000000001E-2</v>
@@ -3924,10 +3935,10 @@
         <v>1010205001</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F65" s="10">
         <v>0.125</v>
@@ -3936,7 +3947,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q65" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="R65" s="10">
         <v>0.05</v>
@@ -3953,10 +3964,10 @@
         <v>1010205001</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F66" s="10">
         <v>0.15</v>
@@ -3965,7 +3976,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q66" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="R66" s="10">
         <v>0.1</v>
@@ -3982,10 +3993,10 @@
         <v>1010205001</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F67" s="10">
         <v>0.17499999999999999</v>
@@ -3994,7 +4005,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q67" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="R67" s="10">
         <v>0.15</v>
@@ -4012,10 +4023,10 @@
         <v>1010205001</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F68" s="10">
         <v>0.2</v>
@@ -4024,7 +4035,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q68" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="R68" s="10">
         <v>0.2</v>
@@ -4041,10 +4052,10 @@
         <v>1010205001</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F69" s="10">
         <v>0.22500000000000001</v>
@@ -4053,7 +4064,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q69" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="R69" s="10">
         <v>0.25</v>
@@ -4070,10 +4081,10 @@
         <v>1010205002</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F70" s="10">
         <v>0.1</v>
@@ -4082,7 +4093,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q70" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="R70" s="10">
         <v>2.5000000000000001E-2</v>
@@ -4099,10 +4110,10 @@
         <v>1010205002</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F71" s="10">
         <v>0.125</v>
@@ -4111,7 +4122,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q71" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="R71" s="10">
         <v>0.05</v>
@@ -4128,10 +4139,10 @@
         <v>1010205002</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F72" s="10">
         <v>0.15</v>
@@ -4140,7 +4151,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q72" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="R72" s="10">
         <v>0.1</v>
@@ -4158,10 +4169,10 @@
         <v>1010205002</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F73" s="10">
         <v>0.17499999999999999</v>
@@ -4170,7 +4181,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q73" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="R73" s="10">
         <v>0.15</v>
@@ -4187,10 +4198,10 @@
         <v>1010205002</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F74" s="10">
         <v>0.2</v>
@@ -4199,7 +4210,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q74" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="R74" s="10">
         <v>0.2</v>
@@ -4216,10 +4227,10 @@
         <v>1010205002</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F75" s="10">
         <v>0.22500000000000001</v>
@@ -4228,7 +4239,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q75" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="R75" s="10">
         <v>0.25</v>
@@ -4245,10 +4256,10 @@
         <v>1010306001</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E76" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F76" s="10">
         <v>0.1</v>
@@ -4257,7 +4268,7 @@
         <v>0.01</v>
       </c>
       <c r="Q76" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R76" s="10">
         <v>0.05</v>
@@ -4274,10 +4285,10 @@
         <v>1010306001</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E77" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F77" s="10">
         <v>0.15</v>
@@ -4286,7 +4297,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q77" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R77" s="10">
         <v>0.1</v>
@@ -4303,10 +4314,10 @@
         <v>1010306001</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E78" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F78" s="10">
         <v>0.2</v>
@@ -4315,7 +4326,7 @@
         <v>0.02</v>
       </c>
       <c r="Q78" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R78" s="10">
         <v>0.15</v>
@@ -4332,10 +4343,10 @@
         <v>1010306001</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E79" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F79" s="10">
         <v>0.25</v>
@@ -4344,7 +4355,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q79" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R79" s="10">
         <v>0.2</v>
@@ -4361,10 +4372,10 @@
         <v>1010306001</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E80" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F80" s="10">
         <v>0.3</v>
@@ -4373,7 +4384,7 @@
         <v>0.03</v>
       </c>
       <c r="Q80" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R80" s="10">
         <v>0.25</v>
@@ -4390,10 +4401,10 @@
         <v>1010306001</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E81" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F81" s="10">
         <v>0.35</v>
@@ -4402,7 +4413,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q81" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R81" s="10">
         <v>0.3</v>
@@ -4419,10 +4430,10 @@
         <v>1010306002</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E82" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F82" s="10">
         <v>0.1</v>
@@ -4431,7 +4442,7 @@
         <v>0.01</v>
       </c>
       <c r="Q82" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R82" s="10">
         <v>0.05</v>
@@ -4448,10 +4459,10 @@
         <v>1010306002</v>
       </c>
       <c r="D83" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E83" t="s">
         <v>54</v>
-      </c>
-      <c r="E83" t="s">
-        <v>63</v>
       </c>
       <c r="F83" s="10">
         <v>0.15</v>
@@ -4460,7 +4471,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q83" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R83" s="10">
         <v>0.1</v>
@@ -4477,10 +4488,10 @@
         <v>1010306002</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E84" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F84" s="10">
         <v>0.2</v>
@@ -4489,7 +4500,7 @@
         <v>0.02</v>
       </c>
       <c r="Q84" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R84" s="10">
         <v>0.15</v>
@@ -4506,10 +4517,10 @@
         <v>1010306002</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E85" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F85" s="10">
         <v>0.25</v>
@@ -4518,7 +4529,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q85" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R85" s="10">
         <v>0.2</v>
@@ -4535,10 +4546,10 @@
         <v>1010306002</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E86" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F86" s="10">
         <v>0.3</v>
@@ -4547,7 +4558,7 @@
         <v>0.03</v>
       </c>
       <c r="Q86" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R86" s="10">
         <v>0.25</v>
@@ -4564,10 +4575,10 @@
         <v>1010306002</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E87" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F87" s="10">
         <v>0.35</v>
@@ -4576,7 +4587,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q87" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R87" s="10">
         <v>0.3</v>
@@ -4593,10 +4604,10 @@
         <v>1010307001</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E88" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F88" s="10">
         <v>0.1</v>
@@ -4605,7 +4616,7 @@
         <v>0.01</v>
       </c>
       <c r="Q88" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R88" s="10">
         <v>0.05</v>
@@ -4622,10 +4633,10 @@
         <v>1010307001</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E89" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F89" s="10">
         <v>0.15</v>
@@ -4634,7 +4645,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q89" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R89" s="10">
         <v>0.1</v>
@@ -4651,10 +4662,10 @@
         <v>1010307001</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E90" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F90" s="10">
         <v>0.2</v>
@@ -4663,7 +4674,7 @@
         <v>0.02</v>
       </c>
       <c r="Q90" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R90" s="10">
         <v>0.15</v>
@@ -4680,10 +4691,10 @@
         <v>1010307001</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E91" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F91" s="10">
         <v>0.25</v>
@@ -4692,7 +4703,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q91" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R91" s="10">
         <v>0.2</v>
@@ -4709,10 +4720,10 @@
         <v>1010307001</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E92" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F92" s="10">
         <v>0.3</v>
@@ -4721,7 +4732,7 @@
         <v>0.03</v>
       </c>
       <c r="Q92" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R92" s="10">
         <v>0.25</v>
@@ -4738,10 +4749,10 @@
         <v>1010307001</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E93" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F93" s="10">
         <v>0.35</v>
@@ -4750,7 +4761,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q93" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R93" s="10">
         <v>0.3</v>
@@ -4767,10 +4778,10 @@
         <v>1010307002</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E94" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F94" s="10">
         <v>0.1</v>
@@ -4779,7 +4790,7 @@
         <v>0.01</v>
       </c>
       <c r="Q94" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R94" s="10">
         <v>0.05</v>
@@ -4796,10 +4807,10 @@
         <v>1010307002</v>
       </c>
       <c r="D95" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E95" t="s">
         <v>54</v>
-      </c>
-      <c r="E95" t="s">
-        <v>63</v>
       </c>
       <c r="F95" s="10">
         <v>0.15</v>
@@ -4808,7 +4819,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q95" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R95" s="10">
         <v>0.1</v>
@@ -4825,10 +4836,10 @@
         <v>1010307002</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E96" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F96" s="10">
         <v>0.2</v>
@@ -4837,7 +4848,7 @@
         <v>0.02</v>
       </c>
       <c r="Q96" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R96" s="10">
         <v>0.15</v>
@@ -4854,10 +4865,10 @@
         <v>1010307002</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E97" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F97" s="10">
         <v>0.25</v>
@@ -4866,7 +4877,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q97" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R97" s="10">
         <v>0.2</v>
@@ -4883,10 +4894,10 @@
         <v>1010307002</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E98" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F98" s="10">
         <v>0.3</v>
@@ -4895,7 +4906,7 @@
         <v>0.03</v>
       </c>
       <c r="Q98" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R98" s="10">
         <v>0.25</v>
@@ -4912,10 +4923,10 @@
         <v>1010307002</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E99" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F99" s="10">
         <v>0.35</v>
@@ -4924,7 +4935,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q99" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R99" s="10">
         <v>0.3</v>
@@ -4941,10 +4952,10 @@
         <v>1010408001</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E100" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F100" s="10">
         <v>0.1</v>
@@ -4953,7 +4964,7 @@
         <v>0.01</v>
       </c>
       <c r="Q100" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R100" s="10">
         <v>0.05</v>
@@ -4970,10 +4981,10 @@
         <v>1010408001</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E101" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F101" s="10">
         <v>0.15</v>
@@ -4982,7 +4993,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q101" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R101" s="10">
         <v>0.1</v>
@@ -4999,10 +5010,10 @@
         <v>1010408001</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E102" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F102" s="10">
         <v>0.2</v>
@@ -5011,7 +5022,7 @@
         <v>0.02</v>
       </c>
       <c r="Q102" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R102" s="10">
         <v>0.15</v>
@@ -5028,10 +5039,10 @@
         <v>1010408001</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E103" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F103" s="10">
         <v>0.25</v>
@@ -5040,7 +5051,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q103" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R103" s="10">
         <v>0.2</v>
@@ -5057,10 +5068,10 @@
         <v>1010408001</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E104" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F104" s="10">
         <v>0.3</v>
@@ -5069,7 +5080,7 @@
         <v>0.03</v>
       </c>
       <c r="Q104" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R104" s="10">
         <v>0.25</v>
@@ -5086,10 +5097,10 @@
         <v>1010408001</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E105" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F105" s="10">
         <v>0.35</v>
@@ -5098,7 +5109,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q105" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R105" s="10">
         <v>0.3</v>
@@ -5115,10 +5126,10 @@
         <v>1010408002</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E106" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F106" s="10">
         <v>0.1</v>
@@ -5127,7 +5138,7 @@
         <v>0.01</v>
       </c>
       <c r="Q106" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R106" s="10">
         <v>0.05</v>
@@ -5144,10 +5155,10 @@
         <v>1010408002</v>
       </c>
       <c r="D107" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E107" t="s">
         <v>54</v>
-      </c>
-      <c r="E107" t="s">
-        <v>63</v>
       </c>
       <c r="F107" s="10">
         <v>0.15</v>
@@ -5156,7 +5167,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q107" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R107" s="10">
         <v>0.1</v>
@@ -5173,10 +5184,10 @@
         <v>1010408002</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E108" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F108" s="10">
         <v>0.2</v>
@@ -5185,7 +5196,7 @@
         <v>0.02</v>
       </c>
       <c r="Q108" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R108" s="10">
         <v>0.15</v>
@@ -5202,10 +5213,10 @@
         <v>1010408002</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E109" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F109" s="10">
         <v>0.25</v>
@@ -5214,7 +5225,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q109" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R109" s="10">
         <v>0.2</v>
@@ -5231,10 +5242,10 @@
         <v>1010408002</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E110" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F110" s="10">
         <v>0.3</v>
@@ -5243,7 +5254,7 @@
         <v>0.03</v>
       </c>
       <c r="Q110" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R110" s="10">
         <v>0.25</v>
@@ -5260,10 +5271,10 @@
         <v>1010408002</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E111" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F111" s="10">
         <v>0.35</v>
@@ -5272,7 +5283,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q111" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R111" s="10">
         <v>0.3</v>
@@ -5304,10 +5315,10 @@
   <sheetData>
     <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="11"/>
@@ -5315,37 +5326,37 @@
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -5492,10 +5503,10 @@
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -5505,55 +5516,55 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>60</v>
-      </c>
       <c r="I2" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -5562,7 +5573,7 @@
         <v>10001</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D4" s="10">
         <v>800</v>
@@ -5589,7 +5600,7 @@
         <v>10002</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D5" s="10">
         <v>400</v>
@@ -5616,7 +5627,7 @@
         <v>10003</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D6" s="10">
         <v>100</v>
@@ -5642,7 +5653,7 @@
         <v>20001</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D7" s="10">
         <v>400</v>
@@ -5668,7 +5679,7 @@
         <v>20002</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D8" s="10">
         <v>100</v>
@@ -5695,7 +5706,7 @@
         <v>20003</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D9" s="10">
         <v>0</v>
@@ -5722,7 +5733,7 @@
         <v>30001</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D10" s="10">
         <v>0</v>
@@ -5748,7 +5759,7 @@
         <v>40001</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D11">
         <v>700</v>
@@ -5774,7 +5785,7 @@
         <v>40002</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -5800,7 +5811,7 @@
         <v>40003</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D13">
         <v>0</v>

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="100">
   <si>
     <t>!Enum</t>
   </si>
@@ -299,6 +299,39 @@
   <si>
     <t>Weapon_Rifle_01</t>
     <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>NormalAttackSkill</t>
+  </si>
+  <si>
+    <t>!Skill</t>
+  </si>
+  <si>
+    <t>AnimControllerName</t>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Attack</t>
+  </si>
+  <si>
+    <t>AOC_Hero_GreatSword</t>
+  </si>
+  <si>
+    <t>Skill_Blade_Attack</t>
+  </si>
+  <si>
+    <t>AOC_Hero_Blade</t>
+  </si>
+  <si>
+    <t>Skill_Pistol_Attack</t>
+  </si>
+  <si>
+    <t>AOC_Hero_Pistol</t>
+  </si>
+  <si>
+    <t>Skill_Rifle_Attack</t>
+  </si>
+  <si>
+    <t>AOC_Hero_Rifle</t>
   </si>
 </sst>
 </file>
@@ -841,7 +874,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1022,7 +1055,12 @@
       <c r="G2" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="I2" s="7"/>
+      <c r="H2" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
       <c r="O2" s="7"/>
@@ -1047,8 +1085,12 @@
       <c r="G3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
+      <c r="H3" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="J3" s="7"/>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -1074,6 +1116,12 @@
       <c r="G4" s="10" t="s">
         <v>82</v>
       </c>
+      <c r="H4" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>93</v>
+      </c>
       <c r="J4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
@@ -1099,6 +1147,12 @@
       <c r="G5" s="10" t="s">
         <v>84</v>
       </c>
+      <c r="H5" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>95</v>
+      </c>
       <c r="J5" s="7"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
@@ -1124,6 +1178,12 @@
       <c r="G6" s="10" t="s">
         <v>86</v>
       </c>
+      <c r="H6" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>97</v>
+      </c>
       <c r="J6" s="7"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
@@ -1148,6 +1208,12 @@
       </c>
       <c r="G7" s="10" t="s">
         <v>88</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>99</v>
       </c>
       <c r="J7" s="7"/>
       <c r="L7" s="7"/>

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -261,10 +261,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Pistol</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>Rifle</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -285,14 +281,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Pistol</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weapon_Pistol_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>Rifle</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -322,16 +310,30 @@
     <t>AOC_Hero_Blade</t>
   </si>
   <si>
-    <t>Skill_Pistol_Attack</t>
-  </si>
-  <si>
-    <t>AOC_Hero_Pistol</t>
-  </si>
-  <si>
     <t>Skill_Rifle_Attack</t>
   </si>
   <si>
     <t>AOC_Hero_Rifle</t>
+  </si>
+  <si>
+    <t>Shuriken</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shuriken</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_Shuriken_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Shuriken_Attack</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOC_Hero_Shuriken</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -970,12 +972,12 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="10" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.3">
@@ -1002,8 +1004,8 @@
     <col min="5" max="5" width="16.25" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.625" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.25" style="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.75" style="10" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.5" style="10" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.875" style="10" customWidth="1"/>
@@ -1053,13 +1055,13 @@
         <v>15</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
@@ -1086,7 +1088,7 @@
         <v>20</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>20</v>
@@ -1114,13 +1116,13 @@
         <v>1010101001</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J4" s="7"/>
       <c r="L4" s="7"/>
@@ -1136,7 +1138,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>21</v>
@@ -1145,13 +1147,13 @@
         <v>1010101002</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J5" s="7"/>
       <c r="L5" s="7"/>
@@ -1167,7 +1169,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>21</v>
@@ -1176,13 +1178,13 @@
         <v>1010101003</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J6" s="7"/>
       <c r="L6" s="7"/>
@@ -1198,7 +1200,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>21</v>
@@ -1207,13 +1209,13 @@
         <v>1010101004</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="J7" s="7"/>
       <c r="L7" s="7"/>
